--- a/diseases/d145/2015-2019.xlsx
+++ b/diseases/d145/2015-2019.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1909,6 +1914,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3042,6 +3052,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4175,6 +4190,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5308,6 +5328,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6589,6 +6614,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7722,6 +7752,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9003,6 +9038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10136,6 +10176,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11269,6 +11314,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12550,6 +12600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13683,6 +13738,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14816,6 +14876,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15704,6 +15769,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16444,6 +16514,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17184,6 +17259,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18072,6 +18152,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18812,6 +18897,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19552,6 +19642,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20440,6 +20535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21180,6 +21280,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22068,6 +22173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22808,6 +22918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23548,6 +23663,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24436,6 +24556,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25176,6 +25301,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25916,6 +26046,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26804,6 +26939,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27544,6 +27684,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28284,6 +28429,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29172,6 +29322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29912,6 +30067,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30652,6 +30812,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31540,6 +31705,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32280,6 +32450,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33020,6 +33195,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33908,6 +34088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34648,6 +34833,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35388,6 +35578,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36276,6 +36471,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37016,6 +37216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37756,6 +37961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38644,6 +38854,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39384,6 +39599,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40272,6 +40492,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41012,6 +41237,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41752,6 +41982,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42640,6 +42875,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43380,6 +43620,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44120,6 +44365,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44860,6 +45110,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45748,6 +46003,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46488,6 +46748,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47376,6 +47641,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48116,6 +48386,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48856,6 +49131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49744,6 +50024,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50484,6 +50769,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51224,6 +51514,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52110,6 +52405,11 @@
       <c r="S341" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO341" t="inlineStr">
